--- a/Output/Models/Exposure_models_malf_iqr_Femenino.xlsx
+++ b/Output/Models/Exposure_models_malf_iqr_Femenino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.146896486853483</v>
+        <v>1.159435203076574</v>
       </c>
       <c r="C3">
-        <v>0.1623620006121416</v>
+        <v>0.161729993313152</v>
       </c>
       <c r="D3">
-        <v>0.84416049752808</v>
+        <v>0.9146911442765399</v>
       </c>
       <c r="E3">
-        <v>0.3985797252745047</v>
+        <v>0.3603537946979234</v>
       </c>
       <c r="F3">
-        <v>0.8342984504000179</v>
+        <v>0.8444650158495084</v>
       </c>
       <c r="G3">
-        <v>1.576619914523615</v>
+        <v>1.591883577060795</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9559126024969273</v>
+        <v>0.9400580056596354</v>
       </c>
       <c r="C4">
-        <v>0.1649232039902122</v>
+        <v>0.1609407959029988</v>
       </c>
       <c r="D4">
-        <v>-0.273392639732894</v>
+        <v>-0.3840772448439028</v>
       </c>
       <c r="E4">
-        <v>0.7845514100021267</v>
+        <v>0.7009211964483505</v>
       </c>
       <c r="F4">
-        <v>0.6918872085128704</v>
+        <v>0.6857433400817785</v>
       </c>
       <c r="G4">
-        <v>1.320690558185758</v>
+        <v>1.28868776749532</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9527729145812176</v>
+        <v>0.8817107178922167</v>
       </c>
       <c r="C5">
-        <v>0.1655698917972457</v>
+        <v>0.1691944929786312</v>
       </c>
       <c r="D5">
-        <v>-0.292194963720288</v>
+        <v>-0.7440624030182265</v>
       </c>
       <c r="E5">
-        <v>0.7701375620685311</v>
+        <v>0.456838723383521</v>
       </c>
       <c r="F5">
-        <v>0.6887411875974813</v>
+        <v>0.6328597953913391</v>
       </c>
       <c r="G5">
-        <v>1.318022274704031</v>
+        <v>1.228413932607745</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="6">
@@ -812,26 +812,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B8">
-        <v>1.005386730468943</v>
+        <v>1.007776295167872</v>
       </c>
       <c r="C8">
-        <v>0.1713316619973203</v>
+        <v>0.2470410136083064</v>
       </c>
       <c r="D8">
-        <v>0.0313559902831845</v>
+        <v>0.03135599028319165</v>
       </c>
       <c r="E8">
-        <v>0.9749856385437347</v>
+        <v>0.9749856385437289</v>
       </c>
       <c r="F8">
-        <v>0.718613503558914</v>
+        <v>0.6209869115037294</v>
       </c>
       <c r="G8">
-        <v>1.406601007074122</v>
+        <v>1.635482233664087</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,26 +875,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B9">
-        <v>1.14909080334431</v>
+        <v>1.249690321259002</v>
       </c>
       <c r="C9">
-        <v>0.1753265436501462</v>
+        <v>0.2536471078782603</v>
       </c>
       <c r="D9">
-        <v>0.7926410970111452</v>
+        <v>0.8787633318296169</v>
       </c>
       <c r="E9">
-        <v>0.4279869574849698</v>
+        <v>0.37952961175553</v>
       </c>
       <c r="F9">
-        <v>0.8149221537339583</v>
+        <v>0.7601470188185637</v>
       </c>
       <c r="G9">
-        <v>1.62028933473017</v>
+        <v>2.05450506334379</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -938,26 +938,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.9801476897947197</v>
+        <v>0.9229065790376197</v>
       </c>
       <c r="C10">
-        <v>0.1782566759897077</v>
+        <v>0.2573624753725321</v>
       </c>
       <c r="D10">
-        <v>-0.1124895586025742</v>
+        <v>-0.3117286774725227</v>
       </c>
       <c r="E10">
-        <v>0.9104352482248108</v>
+        <v>0.7552467317141522</v>
       </c>
       <c r="F10">
-        <v>0.6911290739038465</v>
+        <v>0.5573017486014193</v>
       </c>
       <c r="G10">
-        <v>1.390029055475074</v>
+        <v>1.528357942117451</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1001,26 +1001,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.9312101906933498</v>
+        <v>0.8253100827823208</v>
       </c>
       <c r="C11">
-        <v>0.1757902780189187</v>
+        <v>0.2652126493636578</v>
       </c>
       <c r="D11">
-        <v>-0.4054277588842654</v>
+        <v>-0.723932684987136</v>
       </c>
       <c r="E11">
-        <v>0.6851631099648269</v>
+        <v>0.469107062579142</v>
       </c>
       <c r="F11">
-        <v>0.6598037265526369</v>
+        <v>0.4907583916425196</v>
       </c>
       <c r="G11">
-        <v>1.314258141253415</v>
+        <v>1.387926817639255</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1058,32 +1058,32 @@
         </is>
       </c>
       <c r="O11">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.8671352326446772</v>
+        <v>0.820687115346372</v>
       </c>
       <c r="C12">
-        <v>0.1473701781394546</v>
+        <v>0.204280618250068</v>
       </c>
       <c r="D12">
-        <v>-0.9673621793034913</v>
+        <v>-0.9673621793034948</v>
       </c>
       <c r="E12">
-        <v>0.3333630098805828</v>
+        <v>0.333363009880581</v>
       </c>
       <c r="F12">
-        <v>0.6495986435695511</v>
+        <v>0.5499125581540486</v>
       </c>
       <c r="G12">
-        <v>1.157520138222443</v>
+        <v>1.224789889426151</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1127,26 +1127,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B13">
-        <v>1.058058446371972</v>
+        <v>1.291730185775734</v>
       </c>
       <c r="C13">
-        <v>0.1514231923340942</v>
+        <v>0.686830873675393</v>
       </c>
       <c r="D13">
-        <v>0.3727009935396385</v>
+        <v>0.3727009935396665</v>
       </c>
       <c r="E13">
-        <v>0.709370996915887</v>
+        <v>0.7093709969158661</v>
       </c>
       <c r="F13">
-        <v>0.7863538247169023</v>
+        <v>0.3361555677676987</v>
       </c>
       <c r="G13">
-        <v>1.423643709423174</v>
+        <v>4.963674657911012</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1190,26 +1190,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.9903420435692694</v>
+        <v>0.9863164957967169</v>
       </c>
       <c r="C14">
-        <v>0.1620540656581478</v>
+        <v>0.2300672220194072</v>
       </c>
       <c r="D14">
-        <v>-0.05988678488349829</v>
+        <v>-0.05988678488347779</v>
       </c>
       <c r="E14">
-        <v>0.952245805138942</v>
+        <v>0.9522458051389583</v>
       </c>
       <c r="F14">
-        <v>0.7208494078337899</v>
+        <v>0.6283226595191939</v>
       </c>
       <c r="G14">
-        <v>1.360585654371655</v>
+        <v>1.548281309200496</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1253,26 +1253,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B15">
-        <v>1.146445292765223</v>
+        <v>1.238336467124876</v>
       </c>
       <c r="C15">
-        <v>0.1630817057728937</v>
+        <v>0.2341902509968719</v>
       </c>
       <c r="D15">
-        <v>0.8380222956112586</v>
+        <v>0.9128002521075275</v>
       </c>
       <c r="E15">
-        <v>0.402018181748306</v>
+        <v>0.3613476057161299</v>
       </c>
       <c r="F15">
-        <v>0.8327946678261485</v>
+        <v>0.7825202038119238</v>
       </c>
       <c r="G15">
-        <v>1.578224333177304</v>
+        <v>1.959664681296696</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1316,26 +1316,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.9564413920301421</v>
+        <v>0.9097374725838165</v>
       </c>
       <c r="C16">
-        <v>0.1680767424834992</v>
+        <v>0.2393928092641172</v>
       </c>
       <c r="D16">
-        <v>-0.2649728016031426</v>
+        <v>-0.3951631339717206</v>
       </c>
       <c r="E16">
-        <v>0.7910304143109641</v>
+        <v>0.6927224980656683</v>
       </c>
       <c r="F16">
-        <v>0.6880043439095851</v>
+        <v>0.5690423054601231</v>
       </c>
       <c r="G16">
-        <v>1.329613896316871</v>
+        <v>1.454412547330697</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1379,26 +1379,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.9543962563542948</v>
+        <v>0.8428991454276602</v>
       </c>
       <c r="C17">
-        <v>0.1658076142030021</v>
+        <v>0.2503472810790322</v>
       </c>
       <c r="D17">
-        <v>-0.2815089701564689</v>
+        <v>-0.682683531015043</v>
       </c>
       <c r="E17">
-        <v>0.7783200489708382</v>
+        <v>0.4948068385542627</v>
       </c>
       <c r="F17">
-        <v>0.6895932948544826</v>
+        <v>0.5160355500802098</v>
       </c>
       <c r="G17">
-        <v>1.320883223400982</v>
+        <v>1.37680237195334</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1436,32 +1436,32 @@
         </is>
       </c>
       <c r="O17">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.8609287971065032</v>
+        <v>0.8111141241041123</v>
       </c>
       <c r="C18">
-        <v>0.1362518820328041</v>
+        <v>0.1904848036698446</v>
       </c>
       <c r="D18">
-        <v>-1.099019504478246</v>
+        <v>-1.099019504478241</v>
       </c>
       <c r="E18">
-        <v>0.2717595584556304</v>
+        <v>0.2717595584556326</v>
       </c>
       <c r="F18">
-        <v>0.6591578408284493</v>
+        <v>0.5583943368470548</v>
       </c>
       <c r="G18">
-        <v>1.124462682194132</v>
+        <v>1.178210592242061</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1505,26 +1505,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B19">
-        <v>1.062119625263145</v>
+        <v>1.297083519407669</v>
       </c>
       <c r="C19">
-        <v>0.1436316956382165</v>
+        <v>0.619933067453626</v>
       </c>
       <c r="D19">
-        <v>0.4195909384700977</v>
+        <v>0.4195909384701108</v>
       </c>
       <c r="E19">
-        <v>0.6747843091753463</v>
+        <v>0.6747843091753367</v>
       </c>
       <c r="F19">
-        <v>0.8015191676288832</v>
+        <v>0.384839779877759</v>
       </c>
       <c r="G19">
-        <v>1.407449932490511</v>
+        <v>4.371756102899218</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.061702860750585</v>
+        <v>1.070639072763046</v>
       </c>
       <c r="C21">
-        <v>0.1406726449723314</v>
+        <v>0.1406686169382162</v>
       </c>
       <c r="D21">
-        <v>0.4256271114080196</v>
+        <v>0.4852236122930663</v>
       </c>
       <c r="E21">
-        <v>0.6703795816665613</v>
+        <v>0.6275177343603556</v>
       </c>
       <c r="F21">
-        <v>0.8058648533959465</v>
+        <v>0.812654126587056</v>
       </c>
       <c r="G21">
-        <v>1.398761789617523</v>
+        <v>1.410523846031465</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9144360400312976</v>
+        <v>0.8902377941489347</v>
       </c>
       <c r="C22">
-        <v>0.1461429905565469</v>
+        <v>0.147078157998802</v>
       </c>
       <c r="D22">
-        <v>-0.6120564050325242</v>
+        <v>-0.7905094072996095</v>
       </c>
       <c r="E22">
-        <v>0.5405004394888069</v>
+        <v>0.4292303304797616</v>
       </c>
       <c r="F22">
-        <v>0.6866828408524394</v>
+        <v>0.6672873207371989</v>
       </c>
       <c r="G22">
-        <v>1.217728508069433</v>
+        <v>1.187679288219661</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.835802929207991</v>
+        <v>0.7737986050960862</v>
       </c>
       <c r="C23">
-        <v>0.1497371174663217</v>
+        <v>0.1544124795548319</v>
       </c>
       <c r="D23">
-        <v>-1.197848785482703</v>
+        <v>-1.660770166530035</v>
       </c>
       <c r="E23">
-        <v>0.2309758908147084</v>
+        <v>0.09675961503921054</v>
       </c>
       <c r="F23">
-        <v>0.6232286695695265</v>
+        <v>0.5717310799641423</v>
       </c>
       <c r="G23">
-        <v>1.120883185549164</v>
+        <v>1.047283071065862</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="24">
@@ -1946,26 +1946,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B26">
-        <v>1.006950234590127</v>
+        <v>1.009844875654804</v>
       </c>
       <c r="C26">
-        <v>0.1632918914223337</v>
+        <v>0.2309676700109147</v>
       </c>
       <c r="D26">
-        <v>0.04241602556841537</v>
+        <v>0.04241602556842345</v>
       </c>
       <c r="E26">
-        <v>0.9661670532898746</v>
+        <v>0.9661670532898682</v>
       </c>
       <c r="F26">
-        <v>0.7311621436328141</v>
+        <v>0.6421768254166624</v>
       </c>
       <c r="G26">
-        <v>1.386763228609264</v>
+        <v>1.588015376021393</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2009,26 +2009,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B27">
-        <v>1.152367198589424</v>
+        <v>1.249164898539687</v>
       </c>
       <c r="C27">
-        <v>0.1638361712219968</v>
+        <v>0.2354162895814158</v>
       </c>
       <c r="D27">
-        <v>0.8656101958552233</v>
+        <v>0.9450291110945004</v>
       </c>
       <c r="E27">
-        <v>0.3867039623941851</v>
+        <v>0.344644014113008</v>
       </c>
       <c r="F27">
-        <v>0.8358595062873502</v>
+        <v>0.7874682692788776</v>
       </c>
       <c r="G27">
-        <v>1.588724122171216</v>
+        <v>1.981556596778957</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2072,26 +2072,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.9557642591046172</v>
+        <v>0.8819631129696054</v>
       </c>
       <c r="C28">
-        <v>0.1682720173007527</v>
+        <v>0.2408075066928357</v>
       </c>
       <c r="D28">
-        <v>-0.2688741001610318</v>
+        <v>-0.5215993787106222</v>
       </c>
       <c r="E28">
-        <v>0.7880265683478496</v>
+        <v>0.6019492959819948</v>
       </c>
       <c r="F28">
-        <v>0.6872541724361958</v>
+        <v>0.5501418712975652</v>
       </c>
       <c r="G28">
-        <v>1.329181190335523</v>
+        <v>1.41392424976557</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2135,26 +2135,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.8643126276980478</v>
+        <v>0.7420987013993746</v>
       </c>
       <c r="C29">
-        <v>0.1691914842849568</v>
+        <v>0.2521275856659159</v>
       </c>
       <c r="D29">
-        <v>-0.8618680699463996</v>
+        <v>-1.1830241546936</v>
       </c>
       <c r="E29">
-        <v>0.3887601214966763</v>
+        <v>0.2367995745884725</v>
       </c>
       <c r="F29">
-        <v>0.6203757390985274</v>
+        <v>0.4527414752038849</v>
       </c>
       <c r="G29">
-        <v>1.204167525125706</v>
+        <v>1.216390617560793</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2192,32 +2192,32 @@
         </is>
       </c>
       <c r="O29">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.8359116633715986</v>
+        <v>0.7899710486382278</v>
       </c>
       <c r="C30">
-        <v>0.1491443726615693</v>
+        <v>0.1961818158596902</v>
       </c>
       <c r="D30">
-        <v>-1.201737176571946</v>
+        <v>-1.201737176571943</v>
       </c>
       <c r="E30">
-        <v>0.2294653725767231</v>
+        <v>0.2294653725767244</v>
       </c>
       <c r="F30">
-        <v>0.624034304965609</v>
+        <v>0.5378001399112321</v>
       </c>
       <c r="G30">
-        <v>1.119727398639056</v>
+        <v>1.160383219293297</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2261,26 +2261,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.9870606706269999</v>
+        <v>0.9449672816241553</v>
       </c>
       <c r="C31">
-        <v>0.1344120418961882</v>
+        <v>0.5841925369001133</v>
       </c>
       <c r="D31">
-        <v>-0.09689438178734783</v>
+        <v>-0.09689438178733689</v>
       </c>
       <c r="E31">
-        <v>0.9228102704986784</v>
+        <v>0.922810270498687</v>
       </c>
       <c r="F31">
-        <v>0.7584590021231189</v>
+        <v>0.3007122934442211</v>
       </c>
       <c r="G31">
-        <v>1.284563522578467</v>
+        <v>2.969493375586858</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2324,26 +2324,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.9119596799334226</v>
+        <v>0.9071890345805689</v>
       </c>
       <c r="C32">
-        <v>0.1498672238188714</v>
+        <v>0.1583963879170376</v>
       </c>
       <c r="D32">
-        <v>-0.6149410000136097</v>
+        <v>-0.6149410000136087</v>
       </c>
       <c r="E32">
-        <v>0.5385936849462569</v>
+        <v>0.5385936849462576</v>
       </c>
       <c r="F32">
-        <v>0.6798426792433009</v>
+        <v>0.6650748762614289</v>
       </c>
       <c r="G32">
-        <v>1.223327812766862</v>
+        <v>1.237442540439193</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2387,26 +2387,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B33">
-        <v>1.088629808517671</v>
+        <v>1.106121055424533</v>
       </c>
       <c r="C33">
-        <v>0.1479700384200262</v>
+        <v>0.1567932947624241</v>
       </c>
       <c r="D33">
-        <v>0.5738989459206283</v>
+        <v>0.6432631614187008</v>
       </c>
       <c r="E33">
-        <v>0.5660361864077827</v>
+        <v>0.5200533555803856</v>
       </c>
       <c r="F33">
-        <v>0.8145690349956262</v>
+        <v>0.8134670474496538</v>
       </c>
       <c r="G33">
-        <v>1.454898000142597</v>
+        <v>1.504060666119616</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,26 +2450,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.9236340620931889</v>
+        <v>0.8857138600818709</v>
       </c>
       <c r="C34">
-        <v>0.1528861218983456</v>
+        <v>0.1617700919654306</v>
       </c>
       <c r="D34">
-        <v>-0.5195979955080493</v>
+        <v>-0.7502087442902827</v>
       </c>
       <c r="E34">
-        <v>0.603343795485408</v>
+        <v>0.4531289931563925</v>
       </c>
       <c r="F34">
-        <v>0.6844835852827464</v>
+        <v>0.6450516476055248</v>
       </c>
       <c r="G34">
-        <v>1.246340889688927</v>
+        <v>1.216164697591587</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2513,26 +2513,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.8411905894744119</v>
+        <v>0.7738990391409071</v>
       </c>
       <c r="C35">
-        <v>0.1558288541084865</v>
+        <v>0.1757099832742863</v>
       </c>
       <c r="D35">
-        <v>-1.109788191864379</v>
+        <v>-1.458732449406769</v>
       </c>
       <c r="E35">
-        <v>0.2670903087980459</v>
+        <v>0.1446387612152218</v>
       </c>
       <c r="F35">
-        <v>0.6198015306490329</v>
+        <v>0.5484280996749015</v>
       </c>
       <c r="G35">
-        <v>1.141658374220752</v>
+        <v>1.092066076005676</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2570,32 +2570,32 @@
         </is>
       </c>
       <c r="O35">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.8242720993034799</v>
+        <v>0.820972590122234</v>
       </c>
       <c r="C36">
-        <v>0.1319751944579835</v>
+        <v>0.1347143199098219</v>
       </c>
       <c r="D36">
-        <v>-1.464325070895902</v>
+        <v>-1.464325070895899</v>
       </c>
       <c r="E36">
-        <v>0.1431051501816868</v>
+        <v>0.1431051501816878</v>
       </c>
       <c r="F36">
-        <v>0.6364043075178889</v>
+        <v>0.6304630237091086</v>
       </c>
       <c r="G36">
-        <v>1.067598829335497</v>
+        <v>1.069049204133797</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,26 +2639,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.9286339701335212</v>
+        <v>0.8128266962240849</v>
       </c>
       <c r="C37">
-        <v>0.1241279650004608</v>
+        <v>0.3474302460973541</v>
       </c>
       <c r="D37">
-        <v>-0.5964862307219583</v>
+        <v>-0.5964862307219584</v>
       </c>
       <c r="E37">
-        <v>0.5508504496635335</v>
+        <v>0.5508504496635334</v>
       </c>
       <c r="F37">
-        <v>0.7280926569563159</v>
+        <v>0.4114004831234164</v>
       </c>
       <c r="G37">
-        <v>1.184411135377905</v>
+        <v>1.605946675313846</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.9617302584588874</v>
+        <v>1.028909778719837</v>
       </c>
       <c r="C39">
-        <v>0.3612417794136554</v>
+        <v>0.3595408002780504</v>
       </c>
       <c r="D39">
-        <v>-0.1080197985698962</v>
+        <v>0.07926714961177563</v>
       </c>
       <c r="E39">
-        <v>0.9139799871139367</v>
+        <v>0.9368201348709426</v>
       </c>
       <c r="F39">
-        <v>0.4737658145014629</v>
+        <v>0.5085522858356886</v>
       </c>
       <c r="G39">
-        <v>1.952283304798351</v>
+        <v>2.081704010052079</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.221378032115491</v>
+        <v>1.281932319394207</v>
       </c>
       <c r="C40">
-        <v>0.392578892766893</v>
+        <v>0.3736701247587622</v>
       </c>
       <c r="D40">
-        <v>0.5094001728224649</v>
+        <v>0.6646733245827076</v>
       </c>
       <c r="E40">
-        <v>0.6104717552306294</v>
+        <v>0.5062594591298403</v>
       </c>
       <c r="F40">
-        <v>0.5658304889673736</v>
+        <v>0.6163061621117909</v>
       </c>
       <c r="G40">
-        <v>2.636415545681783</v>
+        <v>2.666451469309381</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.5886525148982</v>
+        <v>1.135252403010689</v>
       </c>
       <c r="C41">
-        <v>0.3709072971684564</v>
+        <v>0.3746872928063005</v>
       </c>
       <c r="D41">
-        <v>1.247983486842104</v>
+        <v>0.3385623429270064</v>
       </c>
       <c r="E41">
-        <v>0.2120371045702531</v>
+        <v>0.7349394548304726</v>
       </c>
       <c r="F41">
-        <v>0.7679130548777306</v>
+        <v>0.544700818654661</v>
       </c>
       <c r="G41">
-        <v>3.286591883106123</v>
+        <v>2.366065873968582</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="42">
@@ -3080,26 +3080,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.7124833911948756</v>
+        <v>0.6133632022740876</v>
       </c>
       <c r="C44">
-        <v>0.4013039568438536</v>
+        <v>0.5786352336048677</v>
       </c>
       <c r="D44">
-        <v>-0.8447429234958048</v>
+        <v>-0.8447429234958245</v>
       </c>
       <c r="E44">
-        <v>0.3982543883354202</v>
+        <v>0.3982543883354092</v>
       </c>
       <c r="F44">
-        <v>0.3244772088471457</v>
+        <v>0.1973251828144247</v>
       </c>
       <c r="G44">
-        <v>1.564462985034136</v>
+        <v>1.906570730294145</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3143,26 +3143,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B45">
-        <v>0.8826094104193375</v>
+        <v>0.9672979622095348</v>
       </c>
       <c r="C45">
-        <v>0.4032892767502168</v>
+        <v>0.5795425336411215</v>
       </c>
       <c r="D45">
-        <v>-0.3096351111868523</v>
+        <v>-0.05737059584880784</v>
       </c>
       <c r="E45">
-        <v>0.7568384527307084</v>
+        <v>0.9542499855243201</v>
       </c>
       <c r="F45">
-        <v>0.4003944960242834</v>
+        <v>0.3106367071210994</v>
       </c>
       <c r="G45">
-        <v>1.945579619839543</v>
+        <v>3.012088804205475</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3206,26 +3206,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B46">
-        <v>1.517582384441017</v>
+        <v>1.599527700188325</v>
       </c>
       <c r="C46">
-        <v>0.4323714155284601</v>
+        <v>0.5934328733762894</v>
       </c>
       <c r="D46">
-        <v>0.9647227293004362</v>
+        <v>0.7915105808255936</v>
       </c>
       <c r="E46">
-        <v>0.3346837076095474</v>
+        <v>0.4286461042174309</v>
       </c>
       <c r="F46">
-        <v>0.6503049512643765</v>
+        <v>0.499874275702933</v>
       </c>
       <c r="G46">
-        <v>3.541502012383407</v>
+        <v>5.118264707804688</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3269,26 +3269,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B47">
-        <v>1.404466349494769</v>
+        <v>1.217190106519318</v>
       </c>
       <c r="C47">
-        <v>0.3912310731275985</v>
+        <v>0.5873462149513781</v>
       </c>
       <c r="D47">
-        <v>0.8681759490521662</v>
+        <v>0.3346322934233027</v>
       </c>
       <c r="E47">
-        <v>0.3852980185405191</v>
+        <v>0.7379024813582894</v>
       </c>
       <c r="F47">
-        <v>0.652371297304036</v>
+        <v>0.3849536210261595</v>
       </c>
       <c r="G47">
-        <v>3.02362433021616</v>
+        <v>3.848650004795852</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,32 +3326,32 @@
         </is>
       </c>
       <c r="O47">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B48">
-        <v>0.8362424596927142</v>
+        <v>0.7804390354846781</v>
       </c>
       <c r="C48">
-        <v>0.2557617774338607</v>
+        <v>0.35453016803362</v>
       </c>
       <c r="D48">
-        <v>-0.6992314730706999</v>
+        <v>-0.6992314730707129</v>
       </c>
       <c r="E48">
-        <v>0.4844073846345535</v>
+        <v>0.4844073846345454</v>
       </c>
       <c r="F48">
-        <v>0.5065559199324143</v>
+        <v>0.389549236398717</v>
       </c>
       <c r="G48">
-        <v>1.380501981866529</v>
+        <v>1.563563809645965</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,26 +3395,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B49">
-        <v>1.696048624149985</v>
+        <v>10.98233425491357</v>
       </c>
       <c r="C49">
-        <v>0.3227748186833141</v>
+        <v>1.46405386981636</v>
       </c>
       <c r="D49">
-        <v>1.636748520264302</v>
+        <v>1.636748520264329</v>
       </c>
       <c r="E49">
-        <v>0.1016830262562522</v>
+        <v>0.1016830262562465</v>
       </c>
       <c r="F49">
-        <v>0.900931714443157</v>
+        <v>0.6230024352727088</v>
       </c>
       <c r="G49">
-        <v>3.192895631672815</v>
+        <v>193.5974225106395</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3458,26 +3458,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B50">
-        <v>0.7022635276512612</v>
+        <v>0.6054483460178788</v>
       </c>
       <c r="C50">
-        <v>0.3666112467799674</v>
+        <v>0.5204758718344304</v>
       </c>
       <c r="D50">
-        <v>-0.9640908537023352</v>
+        <v>-0.9640908537022995</v>
       </c>
       <c r="E50">
-        <v>0.3350003778409009</v>
+        <v>0.3350003778409189</v>
       </c>
       <c r="F50">
-        <v>0.3423261333929849</v>
+        <v>0.2182967308074193</v>
       </c>
       <c r="G50">
-        <v>1.440655603418503</v>
+        <v>1.679217541829199</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3521,26 +3521,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B51">
-        <v>0.9415469681431312</v>
+        <v>1.013624631708006</v>
       </c>
       <c r="C51">
-        <v>0.3586583766320074</v>
+        <v>0.515721548319623</v>
       </c>
       <c r="D51">
-        <v>-0.1679343061529201</v>
+        <v>0.02624022786161461</v>
       </c>
       <c r="E51">
-        <v>0.8666349609690513</v>
+        <v>0.9790657297252577</v>
       </c>
       <c r="F51">
-        <v>0.4661776256420564</v>
+        <v>0.3688877027622088</v>
       </c>
       <c r="G51">
-        <v>1.901658604911702</v>
+        <v>2.78522402972997</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3584,26 +3584,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B52">
-        <v>1.257553559716766</v>
+        <v>1.430851957766425</v>
       </c>
       <c r="C52">
-        <v>0.3905958643889724</v>
+        <v>0.5418721734805328</v>
       </c>
       <c r="D52">
-        <v>0.5867143899829176</v>
+        <v>0.6611707687980343</v>
       </c>
       <c r="E52">
-        <v>0.5573955416461496</v>
+        <v>0.508502805052913</v>
       </c>
       <c r="F52">
-        <v>0.5848583414694921</v>
+        <v>0.4947118027095093</v>
       </c>
       <c r="G52">
-        <v>2.703972643329054</v>
+        <v>4.138444471772973</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3647,26 +3647,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B53">
-        <v>1.511960142283783</v>
+        <v>1.23488498608616</v>
       </c>
       <c r="C53">
-        <v>0.3590889596188062</v>
+        <v>0.5388682764466449</v>
       </c>
       <c r="D53">
-        <v>1.15126601754985</v>
+        <v>0.3915202402695375</v>
       </c>
       <c r="E53">
-        <v>0.2496228129545457</v>
+        <v>0.6954127307173814</v>
       </c>
       <c r="F53">
-        <v>0.747968427134047</v>
+        <v>0.4294780790423121</v>
       </c>
       <c r="G53">
-        <v>3.056310118080837</v>
+        <v>3.550683965667031</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3704,32 +3704,32 @@
         </is>
       </c>
       <c r="O53">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B54">
-        <v>0.8320822108636204</v>
+        <v>0.7733741682416935</v>
       </c>
       <c r="C54">
-        <v>0.2241401808958857</v>
+        <v>0.3133556594997846</v>
       </c>
       <c r="D54">
-        <v>-0.8201297561799287</v>
+        <v>-0.8201297561799001</v>
       </c>
       <c r="E54">
-        <v>0.4121421406488884</v>
+        <v>0.4121421406489047</v>
       </c>
       <c r="F54">
-        <v>0.5362629209854144</v>
+        <v>0.4184666391199657</v>
       </c>
       <c r="G54">
-        <v>1.291084612681103</v>
+        <v>1.429283838160552</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3773,26 +3773,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.71954983992865</v>
+        <v>10.37721316312643</v>
       </c>
       <c r="C55">
-        <v>0.3100490804558212</v>
+        <v>1.338212131062607</v>
       </c>
       <c r="D55">
-        <v>1.748312024669831</v>
+        <v>1.748312024669827</v>
       </c>
       <c r="E55">
-        <v>0.08041001218088914</v>
+        <v>0.08041001218088982</v>
       </c>
       <c r="F55">
-        <v>0.9364843245854643</v>
+        <v>0.7533425655821138</v>
       </c>
       <c r="G55">
-        <v>3.1573957773479</v>
+        <v>142.9449999944637</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.8746941332059327</v>
+        <v>0.9057364851455941</v>
       </c>
       <c r="C57">
-        <v>0.249483229531122</v>
+        <v>0.2475478947287728</v>
       </c>
       <c r="D57">
-        <v>-0.5366333281702187</v>
+        <v>-0.3999503635525357</v>
       </c>
       <c r="E57">
-        <v>0.5915209179221683</v>
+        <v>0.689193076385217</v>
       </c>
       <c r="F57">
-        <v>0.5364085648535033</v>
+        <v>0.557556280813948</v>
       </c>
       <c r="G57">
-        <v>1.426319184284146</v>
+        <v>1.471346676117244</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.9796073545496015</v>
+        <v>0.9774955552264041</v>
       </c>
       <c r="C58">
-        <v>0.2619167491870701</v>
+        <v>0.259719623975423</v>
       </c>
       <c r="D58">
-        <v>-0.07866410334365716</v>
+        <v>-0.08763886943741565</v>
       </c>
       <c r="E58">
-        <v>0.9372997983491127</v>
+        <v>0.930163707675673</v>
       </c>
       <c r="F58">
-        <v>0.5862840724575388</v>
+        <v>0.5875448806498901</v>
       </c>
       <c r="G58">
-        <v>1.636801363313804</v>
+        <v>1.626254592552129</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.8780699739302307</v>
+        <v>0.7022355071932004</v>
       </c>
       <c r="C59">
-        <v>0.2611143391088676</v>
+        <v>0.2742428749979239</v>
       </c>
       <c r="D59">
-        <v>-0.4979772156793745</v>
+        <v>-1.288954000674591</v>
       </c>
       <c r="E59">
-        <v>0.6185001014336328</v>
+        <v>0.19741407883355</v>
       </c>
       <c r="F59">
-        <v>0.526342208088625</v>
+        <v>0.4102483344352359</v>
       </c>
       <c r="G59">
-        <v>1.464839542163441</v>
+        <v>1.20203951160889</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="60">
@@ -4214,26 +4214,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B62">
-        <v>0.7765659077101006</v>
+        <v>0.6992992984330269</v>
       </c>
       <c r="C62">
-        <v>0.3484296552115572</v>
+        <v>0.4928351611702437</v>
       </c>
       <c r="D62">
-        <v>-0.7257526972411728</v>
+        <v>-0.725752697241176</v>
       </c>
       <c r="E62">
-        <v>0.4679903899993693</v>
+        <v>0.4679903899993674</v>
       </c>
       <c r="F62">
-        <v>0.3922784587463065</v>
+        <v>0.2661711878844407</v>
       </c>
       <c r="G62">
-        <v>1.537312578786333</v>
+        <v>1.837236827455695</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4277,26 +4277,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B63">
-        <v>0.989100898568655</v>
+        <v>1.096569248797687</v>
       </c>
       <c r="C63">
-        <v>0.3466909614591004</v>
+        <v>0.493076252186289</v>
       </c>
       <c r="D63">
-        <v>-0.03161008789973517</v>
+        <v>0.186961835763036</v>
       </c>
       <c r="E63">
-        <v>0.9747829984305774</v>
+        <v>0.8516905559204948</v>
       </c>
       <c r="F63">
-        <v>0.5013450311553197</v>
+        <v>0.4171851067341166</v>
       </c>
       <c r="G63">
-        <v>1.951391809538512</v>
+        <v>2.882327527993676</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,26 +4340,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B64">
-        <v>1.242669452312172</v>
+        <v>1.193911927021626</v>
       </c>
       <c r="C64">
-        <v>0.3669746004778699</v>
+        <v>0.5070726573739291</v>
       </c>
       <c r="D64">
-        <v>0.5920351150660744</v>
+        <v>0.3495263385018788</v>
       </c>
       <c r="E64">
-        <v>0.5538270743815654</v>
+        <v>0.7266942009123439</v>
       </c>
       <c r="F64">
-        <v>0.6053217462332587</v>
+        <v>0.4419277389927296</v>
       </c>
       <c r="G64">
-        <v>2.551085232472003</v>
+        <v>3.225472319826351</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4403,26 +4403,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B65">
-        <v>0.9967225810760811</v>
+        <v>0.754465894822027</v>
       </c>
       <c r="C65">
-        <v>0.3467624640596719</v>
+        <v>0.5197315295211148</v>
       </c>
       <c r="D65">
-        <v>-0.009467003396443024</v>
+        <v>-0.5420975795176117</v>
       </c>
       <c r="E65">
-        <v>0.9924465369818662</v>
+        <v>0.5877512860855385</v>
       </c>
       <c r="F65">
-        <v>0.5051374330023237</v>
+        <v>0.2724227248454398</v>
       </c>
       <c r="G65">
-        <v>1.966704185279405</v>
+        <v>2.089468809081734</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4460,32 +4460,32 @@
         </is>
       </c>
       <c r="O65">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B66">
-        <v>0.7686446210829683</v>
+        <v>0.7074333128352192</v>
       </c>
       <c r="C66">
-        <v>0.2564402999487144</v>
+        <v>0.3373169420055881</v>
       </c>
       <c r="D66">
-        <v>-1.026073310537283</v>
+        <v>-1.026073310537268</v>
       </c>
       <c r="E66">
-        <v>0.30485702957928</v>
+        <v>0.304857029579287</v>
       </c>
       <c r="F66">
-        <v>0.4649895719279334</v>
+        <v>0.3652252585331683</v>
       </c>
       <c r="G66">
-        <v>1.27059742666949</v>
+        <v>1.370282806066008</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4529,26 +4529,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B67">
-        <v>1.147094909134646</v>
+        <v>1.815664270312824</v>
       </c>
       <c r="C67">
-        <v>0.2227574381976694</v>
+        <v>0.9681664759960542</v>
       </c>
       <c r="D67">
-        <v>0.6160628411539985</v>
+        <v>0.6160628411540071</v>
       </c>
       <c r="E67">
-        <v>0.537853045597775</v>
+        <v>0.5378530455977693</v>
       </c>
       <c r="F67">
-        <v>0.7412895488021511</v>
+        <v>0.2722267190167067</v>
       </c>
       <c r="G67">
-        <v>1.775050967181266</v>
+        <v>12.10989411472238</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4592,26 +4592,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B68">
-        <v>0.5904238477637717</v>
+        <v>0.5729813564665248</v>
       </c>
       <c r="C68">
-        <v>0.2919132291815484</v>
+        <v>0.3085264403338684</v>
       </c>
       <c r="D68">
-        <v>-1.805038488441084</v>
+        <v>-1.805038488441113</v>
       </c>
       <c r="E68">
-        <v>0.07106865943118029</v>
+        <v>0.07106865943117566</v>
       </c>
       <c r="F68">
-        <v>0.3331861188189679</v>
+        <v>0.3129841242929618</v>
       </c>
       <c r="G68">
-        <v>1.04626303533847</v>
+        <v>1.048959386038743</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4655,26 +4655,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B69">
-        <v>0.8770609012672997</v>
+        <v>0.9123351928315033</v>
       </c>
       <c r="C69">
-        <v>0.2785262602919277</v>
+        <v>0.2932954208099355</v>
       </c>
       <c r="D69">
-        <v>-0.4709747876605139</v>
+        <v>-0.3128170913129134</v>
       </c>
       <c r="E69">
-        <v>0.637658739509431</v>
+        <v>0.754419629611622</v>
       </c>
       <c r="F69">
-        <v>0.508098330976948</v>
+        <v>0.5134532569708753</v>
       </c>
       <c r="G69">
-        <v>1.513950701339162</v>
+        <v>1.621093045527434</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4718,26 +4718,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B70">
-        <v>1.015901210837442</v>
+        <v>0.9808390147257477</v>
       </c>
       <c r="C70">
-        <v>0.2881108227052023</v>
+        <v>0.3005719288564035</v>
       </c>
       <c r="D70">
-        <v>0.05475709261099803</v>
+        <v>-0.06436707576959819</v>
       </c>
       <c r="E70">
-        <v>0.9563319842213863</v>
+        <v>0.9486779453728336</v>
       </c>
       <c r="F70">
-        <v>0.577578609757658</v>
+        <v>0.5441898568551008</v>
       </c>
       <c r="G70">
-        <v>1.786865463411143</v>
+        <v>1.767848409317808</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4781,26 +4781,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B71">
-        <v>0.878294697390916</v>
+        <v>0.706855248922622</v>
       </c>
       <c r="C71">
-        <v>0.2833732300246189</v>
+        <v>0.3275667563472041</v>
       </c>
       <c r="D71">
-        <v>-0.457958203819144</v>
+        <v>-1.05911044750448</v>
       </c>
       <c r="E71">
-        <v>0.646982469595337</v>
+        <v>0.2895494824902091</v>
       </c>
       <c r="F71">
-        <v>0.5040023135907129</v>
+        <v>0.3719676395776237</v>
       </c>
       <c r="G71">
-        <v>1.530551655545446</v>
+        <v>1.343246803665011</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4838,32 +4838,32 @@
         </is>
       </c>
       <c r="O71">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B72">
-        <v>0.7652375376321562</v>
+        <v>0.7609996804692561</v>
       </c>
       <c r="C72">
-        <v>0.2079735061600861</v>
+        <v>0.2122899652217367</v>
       </c>
       <c r="D72">
-        <v>-1.28655323259383</v>
+        <v>-1.286553232593803</v>
       </c>
       <c r="E72">
-        <v>0.1982500533380915</v>
+        <v>0.1982500533381011</v>
       </c>
       <c r="F72">
-        <v>0.5090599097588139</v>
+        <v>0.5019759709261069</v>
       </c>
       <c r="G72">
-        <v>1.150333148958381</v>
+        <v>1.153681744179661</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4907,26 +4907,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B73">
-        <v>0.9616937459679564</v>
+        <v>0.8964385345604137</v>
       </c>
       <c r="C73">
-        <v>0.1740149940702005</v>
+        <v>0.4870624618249</v>
       </c>
       <c r="D73">
-        <v>-0.2244589932859088</v>
+        <v>-0.2244589932858973</v>
       </c>
       <c r="E73">
-        <v>0.8224001714744906</v>
+        <v>0.8224001714744996</v>
       </c>
       <c r="F73">
-        <v>0.683777742838905</v>
+        <v>0.3450898596033789</v>
       </c>
       <c r="G73">
-        <v>1.352566489213399</v>
+        <v>2.32867476073746</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.7377419791847003</v>
+        <v>0.6968693152685278</v>
       </c>
       <c r="C74">
-        <v>0.3179488197832895</v>
+        <v>0.3315157770342978</v>
       </c>
       <c r="D74">
-        <v>-0.9566355283905178</v>
+        <v>-1.089412350326131</v>
       </c>
       <c r="E74">
-        <v>0.3387512497499495</v>
+        <v>0.2759720875543292</v>
       </c>
       <c r="F74">
-        <v>0.3956088244773417</v>
+        <v>0.3638853748766486</v>
       </c>
       <c r="G74">
-        <v>1.375761090694607</v>
+        <v>1.334559935879387</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>1.581824721646421</v>
+        <v>1.32386695468966</v>
       </c>
       <c r="C75">
-        <v>0.3141845271382811</v>
+        <v>0.3104229167932154</v>
       </c>
       <c r="D75">
-        <v>1.459585142415073</v>
+        <v>0.9037894752403007</v>
       </c>
       <c r="E75">
-        <v>0.1444041250521911</v>
+        <v>0.3661070435840828</v>
       </c>
       <c r="F75">
-        <v>0.8545234875570855</v>
+        <v>0.7204633215201119</v>
       </c>
       <c r="G75">
-        <v>2.928145904058163</v>
+        <v>2.43263419714608</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.6698448795700694</v>
+        <v>0.694020303227987</v>
       </c>
       <c r="C76">
-        <v>0.3341986551469446</v>
+        <v>0.3255360930262011</v>
       </c>
       <c r="D76">
-        <v>-1.19901474844738</v>
+        <v>-1.122007885933944</v>
       </c>
       <c r="E76">
-        <v>0.2305222108954553</v>
+        <v>0.2618590869452326</v>
       </c>
       <c r="F76">
-        <v>0.3479395767881472</v>
+        <v>0.3666699767037169</v>
       </c>
       <c r="G76">
-        <v>1.289569202871795</v>
+        <v>1.313617726825422</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.336118001068724</v>
+        <v>1.136287848924522</v>
       </c>
       <c r="C77">
-        <v>0.3081292154311802</v>
+        <v>0.3167691379147655</v>
       </c>
       <c r="D77">
-        <v>0.9404119468576045</v>
+        <v>0.4033431955538849</v>
       </c>
       <c r="E77">
-        <v>0.3470062965021742</v>
+        <v>0.6866957688924433</v>
       </c>
       <c r="F77">
-        <v>0.7304067052773613</v>
+        <v>0.6107366512622031</v>
       </c>
       <c r="G77">
-        <v>2.444133247793742</v>
+        <v>2.114086444534008</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
         </is>
       </c>
       <c r="O77">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B78">
-        <v>0.9058119392393266</v>
+        <v>0.6912593531802701</v>
       </c>
       <c r="C78">
-        <v>0.3909514146279612</v>
+        <v>0.5670514591574007</v>
       </c>
       <c r="D78">
-        <v>-0.2530328919847773</v>
+        <v>-0.6511581787734599</v>
       </c>
       <c r="E78">
-        <v>0.800242795923977</v>
+        <v>0.5149443838436996</v>
       </c>
       <c r="F78">
-        <v>0.4209781868101235</v>
+        <v>0.2274919029290564</v>
       </c>
       <c r="G78">
-        <v>1.949020863730839</v>
+        <v>2.100468136258108</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5279,32 +5279,32 @@
         </is>
       </c>
       <c r="O78">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B79">
-        <v>1.390679962042791</v>
+        <v>1.363297324460637</v>
       </c>
       <c r="C79">
-        <v>0.3632187736849692</v>
+        <v>0.5446653498050006</v>
       </c>
       <c r="D79">
-        <v>0.9079729153653554</v>
+        <v>0.5689847330524677</v>
       </c>
       <c r="E79">
-        <v>0.3638925316110206</v>
+        <v>0.5693665006734822</v>
       </c>
       <c r="F79">
-        <v>0.6824248239330757</v>
+        <v>0.4687816422153676</v>
       </c>
       <c r="G79">
-        <v>2.833998250065129</v>
+        <v>3.964702171565976</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5342,32 +5342,32 @@
         </is>
       </c>
       <c r="O79">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B80">
-        <v>0.8472858379966562</v>
+        <v>0.6690319201216476</v>
       </c>
       <c r="C80">
-        <v>0.3871374461318055</v>
+        <v>0.5985140040761358</v>
       </c>
       <c r="D80">
-        <v>-0.4280577139876666</v>
+        <v>-0.6715356768071533</v>
       </c>
       <c r="E80">
-        <v>0.668609102146505</v>
+        <v>0.5018793395649661</v>
       </c>
       <c r="F80">
-        <v>0.3967326615707941</v>
+        <v>0.2070097471720024</v>
       </c>
       <c r="G80">
-        <v>1.809513964459901</v>
+        <v>2.162234949109663</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5405,32 +5405,32 @@
         </is>
       </c>
       <c r="O80">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B81">
-        <v>1.215547524646977</v>
+        <v>1.089073158273205</v>
       </c>
       <c r="C81">
-        <v>0.38445831783999</v>
+        <v>0.5572468583313558</v>
       </c>
       <c r="D81">
-        <v>0.5077133301526437</v>
+        <v>0.1531224801592226</v>
       </c>
       <c r="E81">
-        <v>0.611654398643721</v>
+        <v>0.8783016883222876</v>
       </c>
       <c r="F81">
-        <v>0.572163869399129</v>
+        <v>0.3653656113466367</v>
       </c>
       <c r="G81">
-        <v>2.582399665024433</v>
+        <v>3.246283468495048</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5468,32 +5468,32 @@
         </is>
       </c>
       <c r="O81">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B82">
-        <v>0.8031586019954789</v>
+        <v>0.6314649620836852</v>
       </c>
       <c r="C82">
-        <v>0.3313219985542536</v>
+        <v>0.4740444371122122</v>
       </c>
       <c r="D82">
-        <v>-0.6616013233946754</v>
+        <v>-0.9697673601395553</v>
       </c>
       <c r="E82">
-        <v>0.508226759187949</v>
+        <v>0.3321624657834524</v>
       </c>
       <c r="F82">
-        <v>0.4195459360488708</v>
+        <v>0.2493686772167722</v>
       </c>
       <c r="G82">
-        <v>1.537528276484585</v>
+        <v>1.599030009662058</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5531,32 +5531,32 @@
         </is>
       </c>
       <c r="O82">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B83">
-        <v>1.45600829723149</v>
+        <v>1.401297019146976</v>
       </c>
       <c r="C83">
-        <v>0.3079023643566218</v>
+        <v>0.4528549285581959</v>
       </c>
       <c r="D83">
-        <v>1.220187604571665</v>
+        <v>0.7450470972249665</v>
       </c>
       <c r="E83">
-        <v>0.2223937647081889</v>
+        <v>0.4562432486943808</v>
       </c>
       <c r="F83">
-        <v>0.7963003051671336</v>
+        <v>0.5768453341097405</v>
       </c>
       <c r="G83">
-        <v>2.662262148903722</v>
+        <v>3.404089830943549</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5594,32 +5594,32 @@
         </is>
       </c>
       <c r="O83">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B84">
-        <v>0.7379285527786089</v>
+        <v>0.6093824997688372</v>
       </c>
       <c r="C84">
-        <v>0.3336410411992081</v>
+        <v>0.4970194437353593</v>
       </c>
       <c r="D84">
-        <v>-0.9108839545908656</v>
+        <v>-0.996558859489059</v>
       </c>
       <c r="E84">
-        <v>0.3623565207791227</v>
+        <v>0.3189786836662203</v>
       </c>
       <c r="F84">
-        <v>0.3837236313499252</v>
+        <v>0.2300521309746205</v>
       </c>
       <c r="G84">
-        <v>1.419090471676885</v>
+        <v>1.614186443095735</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5657,32 +5657,32 @@
         </is>
       </c>
       <c r="O84">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B85">
-        <v>1.258013855597745</v>
+        <v>1.138263033284157</v>
       </c>
       <c r="C85">
-        <v>0.3230466744495294</v>
+        <v>0.4734571761168234</v>
       </c>
       <c r="D85">
-        <v>0.7105294385010755</v>
+        <v>0.2735272628285922</v>
       </c>
       <c r="E85">
-        <v>0.4773758821898416</v>
+        <v>0.7844479383725951</v>
       </c>
       <c r="F85">
-        <v>0.6678940839084595</v>
+        <v>0.4500234583268631</v>
       </c>
       <c r="G85">
-        <v>2.36953567789472</v>
+        <v>2.879055989121778</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.6624918903769711</v>
+        <v>0.7117982644001639</v>
       </c>
       <c r="C86">
-        <v>0.2443742928620698</v>
+        <v>0.2694890830320226</v>
       </c>
       <c r="D86">
-        <v>-1.684902930315591</v>
+        <v>-1.261500987013129</v>
       </c>
       <c r="E86">
-        <v>0.09200730113628557</v>
+        <v>0.2071284046013194</v>
       </c>
       <c r="F86">
-        <v>0.410363562296628</v>
+        <v>0.4197274775835586</v>
       </c>
       <c r="G86">
-        <v>1.069528450233114</v>
+        <v>1.207108889129665</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.303315284191488</v>
+        <v>1.146348517377774</v>
       </c>
       <c r="C87">
-        <v>0.2720505936989664</v>
+        <v>0.2622806081052412</v>
       </c>
       <c r="D87">
-        <v>0.973757245609907</v>
+        <v>0.5207464228130119</v>
       </c>
       <c r="E87">
-        <v>0.3301770861437771</v>
+        <v>0.6025434305698045</v>
       </c>
       <c r="F87">
-        <v>0.7646797740259685</v>
+        <v>0.6855876966159873</v>
       </c>
       <c r="G87">
-        <v>2.221362180228732</v>
+        <v>1.916771449926247</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.6607585958801889</v>
+        <v>0.712150446580137</v>
       </c>
       <c r="C88">
-        <v>0.2919001723426309</v>
+        <v>0.2742408354139262</v>
       </c>
       <c r="D88">
-        <v>-1.419549406152301</v>
+        <v>-1.237839317409392</v>
       </c>
       <c r="E88">
-        <v>0.1557389036279974</v>
+        <v>0.2157756466116459</v>
       </c>
       <c r="F88">
-        <v>0.3728867438718359</v>
+        <v>0.4160423383515602</v>
       </c>
       <c r="G88">
-        <v>1.17087005425868</v>
+        <v>1.219006365010223</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.018175707469958</v>
+        <v>0.9263230295421173</v>
       </c>
       <c r="C89">
-        <v>0.248505743483568</v>
+        <v>0.2716574024991475</v>
       </c>
       <c r="D89">
-        <v>0.07248324984429921</v>
+        <v>-0.2817234519134871</v>
       </c>
       <c r="E89">
-        <v>0.9422173350913639</v>
+        <v>0.7781555705327245</v>
       </c>
       <c r="F89">
-        <v>0.6255964256224374</v>
+        <v>0.543910272383465</v>
       </c>
       <c r="G89">
-        <v>1.65710948596054</v>
+        <v>1.577602774994349</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,32 +5972,32 @@
         </is>
       </c>
       <c r="O89">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B90">
-        <v>0.8063383053438505</v>
+        <v>0.6938222535696252</v>
       </c>
       <c r="C90">
-        <v>0.3039309175291551</v>
+        <v>0.4559926447097072</v>
       </c>
       <c r="D90">
-        <v>-0.7082263713469197</v>
+        <v>-0.8016345752414765</v>
       </c>
       <c r="E90">
-        <v>0.4788046920203978</v>
+        <v>0.422764371245378</v>
       </c>
       <c r="F90">
-        <v>0.4444376325896057</v>
+        <v>0.2838615581713497</v>
       </c>
       <c r="G90">
-        <v>1.462930712857008</v>
+        <v>1.695859498022794</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6035,32 +6035,32 @@
         </is>
       </c>
       <c r="O90">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B91">
-        <v>1.189984293469529</v>
+        <v>1.138513197816551</v>
       </c>
       <c r="C91">
-        <v>0.3117125284774568</v>
+        <v>0.4464935974071644</v>
       </c>
       <c r="D91">
-        <v>0.5580144921374619</v>
+        <v>0.2905376459883242</v>
       </c>
       <c r="E91">
-        <v>0.5768344881877507</v>
+        <v>0.7714049548371655</v>
       </c>
       <c r="F91">
-        <v>0.6459680587544614</v>
+        <v>0.4745500573728154</v>
       </c>
       <c r="G91">
-        <v>2.192155787756116</v>
+        <v>2.731455368014295</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6098,32 +6098,32 @@
         </is>
       </c>
       <c r="O91">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B92">
-        <v>0.7853139381785009</v>
+        <v>0.6492269102075132</v>
       </c>
       <c r="C92">
-        <v>0.3312959140025742</v>
+        <v>0.4749846689710133</v>
       </c>
       <c r="D92">
-        <v>-0.7294738923298044</v>
+        <v>-0.9094461802321144</v>
       </c>
       <c r="E92">
-        <v>0.465711832198045</v>
+        <v>0.3631146546800404</v>
       </c>
       <c r="F92">
-        <v>0.4102453926891214</v>
+        <v>0.2559109267947879</v>
       </c>
       <c r="G92">
-        <v>1.503290451246498</v>
+        <v>1.647040187836868</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6161,32 +6161,32 @@
         </is>
       </c>
       <c r="O92">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B93">
-        <v>0.9666106844142873</v>
+        <v>0.8484039668977275</v>
       </c>
       <c r="C93">
-        <v>0.3083264592909331</v>
+        <v>0.4638994184531114</v>
       </c>
       <c r="D93">
-        <v>-0.1101412642484778</v>
+        <v>-0.3543836746138578</v>
       </c>
       <c r="E93">
-        <v>0.9122973430757008</v>
+        <v>0.7230513675129711</v>
       </c>
       <c r="F93">
-        <v>0.5282063687573717</v>
+        <v>0.3417675220394304</v>
       </c>
       <c r="G93">
-        <v>1.768884796716714</v>
+        <v>2.106078678139454</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6224,32 +6224,32 @@
         </is>
       </c>
       <c r="O93">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B94">
-        <v>0.6705008963932585</v>
+        <v>0.6677994750882643</v>
       </c>
       <c r="C94">
-        <v>0.2446838109667115</v>
+        <v>0.2797581345263678</v>
       </c>
       <c r="D94">
-        <v>-1.633660346302937</v>
+        <v>-1.443272912109678</v>
       </c>
       <c r="E94">
-        <v>0.1023301889926123</v>
+        <v>0.1489436072757182</v>
       </c>
       <c r="F94">
-        <v>0.4150726572132858</v>
+        <v>0.3859362010012852</v>
       </c>
       <c r="G94">
-        <v>1.083115074557055</v>
+        <v>1.155517771515495</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6287,32 +6287,32 @@
         </is>
       </c>
       <c r="O94">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B95">
-        <v>1.184975188088074</v>
+        <v>1.127207022957209</v>
       </c>
       <c r="C95">
-        <v>0.2587885734685067</v>
+        <v>0.2690932622330735</v>
       </c>
       <c r="D95">
-        <v>0.6558320321907037</v>
+        <v>0.4449866601411199</v>
       </c>
       <c r="E95">
-        <v>0.5119322038297754</v>
+        <v>0.6563293944574522</v>
       </c>
       <c r="F95">
-        <v>0.7135559366697544</v>
+        <v>0.6651982313896927</v>
       </c>
       <c r="G95">
-        <v>1.967843198022802</v>
+        <v>1.910100797997615</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6350,32 +6350,32 @@
         </is>
       </c>
       <c r="O95">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B96">
-        <v>0.6817888234572732</v>
+        <v>0.6594148820463115</v>
       </c>
       <c r="C96">
-        <v>0.2787340096028623</v>
+        <v>0.2850298539205739</v>
       </c>
       <c r="D96">
-        <v>-1.374196541922695</v>
+        <v>-1.460907949813785</v>
       </c>
       <c r="E96">
-        <v>0.1693806740326996</v>
+        <v>0.1440407046428769</v>
       </c>
       <c r="F96">
-        <v>0.3948126492875832</v>
+        <v>0.3771732576539688</v>
       </c>
       <c r="G96">
-        <v>1.177358427167982</v>
+        <v>1.152860065872105</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6413,32 +6413,32 @@
         </is>
       </c>
       <c r="O96">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B97">
-        <v>0.9263550054812244</v>
+        <v>0.9037458317932144</v>
       </c>
       <c r="C97">
-        <v>0.2480159767117606</v>
+        <v>0.2896199388438341</v>
       </c>
       <c r="D97">
-        <v>-0.3084387690260519</v>
+        <v>-0.3494480319535635</v>
       </c>
       <c r="E97">
-        <v>0.7577484855458554</v>
+        <v>0.7267529790061643</v>
       </c>
       <c r="F97">
-        <v>0.5697257783656391</v>
+        <v>0.5122964759285378</v>
       </c>
       <c r="G97">
-        <v>1.506222166463715</v>
+        <v>1.59430440547778</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>1.062700417543788</v>
+        <v>0.6386484952367154</v>
       </c>
       <c r="C98">
-        <v>0.6538859269326585</v>
+        <v>0.6642614440721761</v>
       </c>
       <c r="D98">
-        <v>0.09300281562892213</v>
+        <v>-0.6750370139051277</v>
       </c>
       <c r="E98">
-        <v>0.9259013243712858</v>
+        <v>0.4996522490312515</v>
       </c>
       <c r="F98">
-        <v>0.2950000850076791</v>
+        <v>0.1737166824933143</v>
       </c>
       <c r="G98">
-        <v>3.828243566161496</v>
+        <v>2.347914400701374</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>1.522167454240952</v>
+        <v>1.126575530345199</v>
       </c>
       <c r="C99">
-        <v>0.4891615514336585</v>
+        <v>0.5638061572820886</v>
       </c>
       <c r="D99">
-        <v>0.8588885914141258</v>
+        <v>0.2113891907520302</v>
       </c>
       <c r="E99">
-        <v>0.3904019842317561</v>
+        <v>0.8325835907064654</v>
       </c>
       <c r="F99">
-        <v>0.5835624843553247</v>
+        <v>0.3731192388561689</v>
       </c>
       <c r="G99">
-        <v>3.970429595572819</v>
+        <v>3.401519657531815</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>1.230861710577596</v>
+        <v>0.9066966723264753</v>
       </c>
       <c r="C100">
-        <v>0.6073942004331916</v>
+        <v>0.7050430712569498</v>
       </c>
       <c r="D100">
-        <v>0.3419764325236281</v>
+        <v>-0.138923873481181</v>
       </c>
       <c r="E100">
-        <v>0.7323686282914366</v>
+        <v>0.889510305584974</v>
       </c>
       <c r="F100">
-        <v>0.3742780698828967</v>
+        <v>0.2276817765933755</v>
       </c>
       <c r="G100">
-        <v>4.047847502900775</v>
+        <v>3.610736300060227</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>2.134601954959441</v>
+        <v>1.196928773049181</v>
       </c>
       <c r="C101">
-        <v>0.6019169932602914</v>
+        <v>0.5981685388803379</v>
       </c>
       <c r="D101">
-        <v>1.259775350806312</v>
+        <v>0.3005155045233783</v>
       </c>
       <c r="E101">
-        <v>0.2077504141853447</v>
+        <v>0.7637839717554402</v>
       </c>
       <c r="F101">
-        <v>0.6560912250487451</v>
+        <v>0.3706007754783855</v>
       </c>
       <c r="G101">
-        <v>6.944957243984073</v>
+        <v>3.865719077095062</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,32 +6728,32 @@
         </is>
       </c>
       <c r="O101">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B102">
-        <v>1.362453461384666</v>
+        <v>0.8304388791686169</v>
       </c>
       <c r="C102">
-        <v>0.7505178783049135</v>
+        <v>1.101923617107035</v>
       </c>
       <c r="D102">
-        <v>0.412098231275385</v>
+        <v>-0.1686150881730429</v>
       </c>
       <c r="E102">
-        <v>0.6802674250340457</v>
+        <v>0.8660994118513623</v>
       </c>
       <c r="F102">
-        <v>0.3129534188629786</v>
+        <v>0.09579626798279908</v>
       </c>
       <c r="G102">
-        <v>5.931487954927244</v>
+        <v>7.19891021389953</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6791,32 +6791,32 @@
         </is>
       </c>
       <c r="O102">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B103">
-        <v>1.260875162850812</v>
+        <v>1.29178936649969</v>
       </c>
       <c r="C103">
-        <v>0.5640583691594186</v>
+        <v>0.9704227592517367</v>
       </c>
       <c r="D103">
-        <v>0.410961110098028</v>
+        <v>0.2638317790919724</v>
       </c>
       <c r="E103">
-        <v>0.6811010514271889</v>
+        <v>0.7919095457248226</v>
       </c>
       <c r="F103">
-        <v>0.4173925908643153</v>
+        <v>0.1928263386527598</v>
       </c>
       <c r="G103">
-        <v>3.808898890615121</v>
+        <v>8.654003281194321</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6854,32 +6854,32 @@
         </is>
       </c>
       <c r="O103">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B104">
-        <v>1.826643456132738</v>
+        <v>1.474968705914825</v>
       </c>
       <c r="C104">
-        <v>0.6853798807791884</v>
+        <v>1.190611845148935</v>
       </c>
       <c r="D104">
-        <v>0.8790455083529269</v>
+        <v>0.3264176942479238</v>
       </c>
       <c r="E104">
-        <v>0.3793766014919969</v>
+        <v>0.744108351961867</v>
       </c>
       <c r="F104">
-        <v>0.4767134147318247</v>
+        <v>0.1429987252895702</v>
       </c>
       <c r="G104">
-        <v>6.999228913475354</v>
+        <v>15.21365088410846</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6917,32 +6917,32 @@
         </is>
       </c>
       <c r="O104">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B105">
-        <v>1.799277329125451</v>
+        <v>1.491693025283419</v>
       </c>
       <c r="C105">
-        <v>0.6741152835186763</v>
+        <v>0.9994649738084063</v>
       </c>
       <c r="D105">
-        <v>0.8713422093039445</v>
+        <v>0.4001258112726127</v>
       </c>
       <c r="E105">
-        <v>0.3835673300895522</v>
+        <v>0.6890638540411855</v>
       </c>
       <c r="F105">
-        <v>0.4800540502856382</v>
+        <v>0.210345551135189</v>
       </c>
       <c r="G105">
-        <v>6.743821670035952</v>
+        <v>10.57853645903401</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6980,32 +6980,32 @@
         </is>
       </c>
       <c r="O105">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B106">
-        <v>1.066903063469911</v>
+        <v>0.5869901083232704</v>
       </c>
       <c r="C106">
-        <v>0.6558594401707767</v>
+        <v>0.9450289707868339</v>
       </c>
       <c r="D106">
-        <v>0.09874084997422944</v>
+        <v>-0.5637364853381137</v>
       </c>
       <c r="E106">
-        <v>0.9213440337403704</v>
+        <v>0.5729334829948014</v>
       </c>
       <c r="F106">
-        <v>0.2950233529983525</v>
+        <v>0.09209173698348705</v>
       </c>
       <c r="G106">
-        <v>3.858278116877881</v>
+        <v>3.741458230190045</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7043,32 +7043,32 @@
         </is>
       </c>
       <c r="O106">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B107">
-        <v>1.37360939262677</v>
+        <v>1.197168443207195</v>
       </c>
       <c r="C107">
-        <v>0.4864807022004928</v>
+        <v>0.8324374667385485</v>
       </c>
       <c r="D107">
-        <v>0.652527154942521</v>
+        <v>0.2161833711339315</v>
       </c>
       <c r="E107">
-        <v>0.5140611609567405</v>
+        <v>0.8288448149933829</v>
       </c>
       <c r="F107">
-        <v>0.529383166535472</v>
+        <v>0.2341980119893101</v>
       </c>
       <c r="G107">
-        <v>3.564153306688222</v>
+        <v>6.119660321781712</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7106,32 +7106,32 @@
         </is>
       </c>
       <c r="O107">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B108">
-        <v>1.295440474722033</v>
+        <v>0.9582410073176986</v>
       </c>
       <c r="C108">
-        <v>0.6062708250699252</v>
+        <v>1.03913775335327</v>
       </c>
       <c r="D108">
-        <v>0.4269556797646769</v>
+        <v>-0.04104937878773825</v>
       </c>
       <c r="E108">
-        <v>0.6694116092146627</v>
+        <v>0.9672565304316016</v>
       </c>
       <c r="F108">
-        <v>0.3947833246506429</v>
+        <v>0.1250141271584369</v>
       </c>
       <c r="G108">
-        <v>4.250853363761279</v>
+        <v>7.344976515666286</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7169,32 +7169,32 @@
         </is>
       </c>
       <c r="O108">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B109">
-        <v>1.875135092192996</v>
+        <v>1.357352750372635</v>
       </c>
       <c r="C109">
-        <v>0.5889510787509696</v>
+        <v>0.8803606072181838</v>
       </c>
       <c r="D109">
-        <v>1.067458280796163</v>
+        <v>0.3470581182949586</v>
       </c>
       <c r="E109">
-        <v>0.2857649429481988</v>
+        <v>0.7285476569282519</v>
       </c>
       <c r="F109">
-        <v>0.5911755912374025</v>
+        <v>0.2417288131982529</v>
       </c>
       <c r="G109">
-        <v>5.947694164121264</v>
+        <v>7.621790983738103</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.5688737435234449</v>
+        <v>0.6219885432179941</v>
       </c>
       <c r="C110">
-        <v>0.321963401635584</v>
+        <v>0.3698860572511807</v>
       </c>
       <c r="D110">
-        <v>-1.752052433556918</v>
+        <v>-1.283729398196324</v>
       </c>
       <c r="E110">
-        <v>0.07976479230921311</v>
+        <v>0.1992366543548453</v>
       </c>
       <c r="F110">
-        <v>0.3026635662110121</v>
+        <v>0.3012553737168598</v>
       </c>
       <c r="G110">
-        <v>1.06923122634707</v>
+        <v>1.284192023270094</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.162046471226465</v>
+        <v>1.071421916042532</v>
       </c>
       <c r="C111">
-        <v>0.3449826042172101</v>
+        <v>0.3492462673348619</v>
       </c>
       <c r="D111">
-        <v>0.4353339798696332</v>
+        <v>0.1975301276674111</v>
       </c>
       <c r="E111">
-        <v>0.663320023812815</v>
+        <v>0.8434127073902764</v>
       </c>
       <c r="F111">
-        <v>0.5909813436638821</v>
+        <v>0.5403579730828042</v>
       </c>
       <c r="G111">
-        <v>2.28493169161341</v>
+        <v>2.124415626972418</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.8806235445464476</v>
+        <v>0.9516871581529578</v>
       </c>
       <c r="C112">
-        <v>0.3632929848997496</v>
+        <v>0.3580345546244105</v>
       </c>
       <c r="D112">
-        <v>-0.3499243155391534</v>
+        <v>-0.1383076380271026</v>
       </c>
       <c r="E112">
-        <v>0.7263954981277028</v>
+        <v>0.889997289254205</v>
       </c>
       <c r="F112">
-        <v>0.4320706271529934</v>
+        <v>0.4717746962242257</v>
       </c>
       <c r="G112">
-        <v>1.794840423010173</v>
+        <v>1.919790218173945</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.9849306455881388</v>
+        <v>0.8412530849341696</v>
       </c>
       <c r="C113">
-        <v>0.3200806504229002</v>
+        <v>0.3665138067039525</v>
       </c>
       <c r="D113">
-        <v>-0.04743820296336123</v>
+        <v>-0.471640434232926</v>
       </c>
       <c r="E113">
-        <v>0.9621639817179259</v>
+        <v>0.6371834604816109</v>
       </c>
       <c r="F113">
-        <v>0.5259597459229722</v>
+        <v>0.4101564560623067</v>
       </c>
       <c r="G113">
-        <v>1.844415630926894</v>
+        <v>1.725455597372701</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,32 +7484,32 @@
         </is>
       </c>
       <c r="O113">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B114">
-        <v>0.8099718305921662</v>
+        <v>0.6899015670014633</v>
       </c>
       <c r="C114">
-        <v>0.4207064328771897</v>
+        <v>0.6504312989257965</v>
       </c>
       <c r="D114">
-        <v>-0.5009569440755836</v>
+        <v>-0.5707080035968688</v>
       </c>
       <c r="E114">
-        <v>0.6164014250722358</v>
+        <v>0.5681975925483991</v>
       </c>
       <c r="F114">
-        <v>0.3551108568379697</v>
+        <v>0.1928141960794161</v>
       </c>
       <c r="G114">
-        <v>1.847463556013355</v>
+        <v>2.468512079655354</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7547,32 +7547,32 @@
         </is>
       </c>
       <c r="O114">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B115">
-        <v>0.9695947523326535</v>
+        <v>0.9581354550616871</v>
       </c>
       <c r="C115">
-        <v>0.4213541335122171</v>
+        <v>0.6234646310481922</v>
       </c>
       <c r="D115">
-        <v>-0.07328058140198294</v>
+        <v>-0.06859429594575893</v>
       </c>
       <c r="E115">
-        <v>0.9415828439448266</v>
+        <v>0.9453125593499709</v>
       </c>
       <c r="F115">
-        <v>0.4245540299478498</v>
+        <v>0.2823142858197995</v>
       </c>
       <c r="G115">
-        <v>2.214356518689738</v>
+        <v>3.251778589880635</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7610,32 +7610,32 @@
         </is>
       </c>
       <c r="O115">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B116">
-        <v>1.146376964320021</v>
+        <v>0.9874001945236787</v>
       </c>
       <c r="C116">
-        <v>0.4552652765870643</v>
+        <v>0.6545027959286365</v>
       </c>
       <c r="D116">
-        <v>0.3000591312942194</v>
+        <v>-0.01937326506520043</v>
       </c>
       <c r="E116">
-        <v>0.7641320521119211</v>
+        <v>0.9845433377926829</v>
       </c>
       <c r="F116">
-        <v>0.4696831116896388</v>
+        <v>0.2737659419940537</v>
       </c>
       <c r="G116">
-        <v>2.798014473196519</v>
+        <v>3.56128719680761</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7673,32 +7673,32 @@
         </is>
       </c>
       <c r="O116">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B117">
-        <v>0.9050791015774623</v>
+        <v>0.7564056198242676</v>
       </c>
       <c r="C117">
-        <v>0.4137219340924927</v>
+        <v>0.6423705737821911</v>
       </c>
       <c r="D117">
-        <v>-0.2410627182786602</v>
+        <v>-0.4346050767592752</v>
       </c>
       <c r="E117">
-        <v>0.8095065072895398</v>
+        <v>0.6638491093949246</v>
       </c>
       <c r="F117">
-        <v>0.4022775424494099</v>
+        <v>0.2147671841771507</v>
       </c>
       <c r="G117">
-        <v>2.03632590356516</v>
+        <v>2.664045086281883</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7736,32 +7736,32 @@
         </is>
       </c>
       <c r="O117">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B118">
-        <v>0.5611377336443576</v>
+        <v>0.563960909946665</v>
       </c>
       <c r="C118">
-        <v>0.3350623370044973</v>
+        <v>0.3990691063707456</v>
       </c>
       <c r="D118">
-        <v>-1.724422070952938</v>
+        <v>-1.435266046274992</v>
       </c>
       <c r="E118">
-        <v>0.08463167601424511</v>
+        <v>0.151211299324421</v>
       </c>
       <c r="F118">
-        <v>0.2909805064553881</v>
+        <v>0.2579649865490015</v>
       </c>
       <c r="G118">
-        <v>1.082119073731839</v>
+        <v>1.232926654902661</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7799,32 +7799,32 @@
         </is>
       </c>
       <c r="O118">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B119">
-        <v>1.041491329411357</v>
+        <v>1.041885685643467</v>
       </c>
       <c r="C119">
-        <v>0.3428166597337914</v>
+        <v>0.3739468975951873</v>
       </c>
       <c r="D119">
-        <v>0.1185871673176313</v>
+        <v>0.1097274262754853</v>
       </c>
       <c r="E119">
-        <v>0.905602432601639</v>
+        <v>0.9126255487237932</v>
       </c>
       <c r="F119">
-        <v>0.5319240038282423</v>
+        <v>0.5006288750423747</v>
       </c>
       <c r="G119">
-        <v>2.039208949835782</v>
+        <v>2.168324353757812</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7862,32 +7862,32 @@
         </is>
       </c>
       <c r="O119">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B120">
-        <v>0.8994006980235554</v>
+        <v>0.8489158229486942</v>
       </c>
       <c r="C120">
-        <v>0.3626370960187663</v>
+        <v>0.3850259959949761</v>
       </c>
       <c r="D120">
-        <v>-0.292376675499345</v>
+        <v>-0.4254134727536329</v>
       </c>
       <c r="E120">
-        <v>0.7699986397460054</v>
+        <v>0.6705352863165202</v>
       </c>
       <c r="F120">
-        <v>0.4418511244285769</v>
+        <v>0.39914427685744</v>
       </c>
       <c r="G120">
-        <v>1.830756041758171</v>
+        <v>1.805507722988226</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7925,32 +7925,32 @@
         </is>
       </c>
       <c r="O120">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B121">
-        <v>0.8738287099698319</v>
+        <v>0.8343946077216355</v>
       </c>
       <c r="C121">
-        <v>0.3291608741003724</v>
+        <v>0.4051895792591283</v>
       </c>
       <c r="D121">
-        <v>-0.4097416101436846</v>
+        <v>-0.4468250099362923</v>
       </c>
       <c r="E121">
-        <v>0.6819955029052038</v>
+        <v>0.6550014119930653</v>
       </c>
       <c r="F121">
-        <v>0.4583994263929629</v>
+        <v>0.3771147278075925</v>
       </c>
       <c r="G121">
-        <v>1.665745134927295</v>
+        <v>1.846160624493449</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>1.462434940817848</v>
+        <v>1.196761969321836</v>
       </c>
       <c r="C122">
-        <v>0.3045422609024674</v>
+        <v>0.2979207083669589</v>
       </c>
       <c r="D122">
-        <v>1.248111881408965</v>
+        <v>0.602910592376623</v>
       </c>
       <c r="E122">
-        <v>0.2119900877595166</v>
+        <v>0.5465681690289872</v>
       </c>
       <c r="F122">
-        <v>0.8050997880658934</v>
+        <v>0.6674476572514626</v>
       </c>
       <c r="G122">
-        <v>2.656460711861297</v>
+        <v>2.145844989722513</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.8715201793577297</v>
+        <v>0.9410860746342278</v>
       </c>
       <c r="C123">
-        <v>0.1875555581224328</v>
+        <v>0.1640920977046012</v>
       </c>
       <c r="D123">
-        <v>-0.7332027956125527</v>
+        <v>-0.3700401968141147</v>
       </c>
       <c r="E123">
-        <v>0.4634347505241114</v>
+        <v>0.7113525401105547</v>
       </c>
       <c r="F123">
-        <v>0.6034341254608089</v>
+        <v>0.6822662688646615</v>
       </c>
       <c r="G123">
-        <v>1.258708102475486</v>
+        <v>1.298089969102871</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.327483921899369</v>
+        <v>1.02983144480188</v>
       </c>
       <c r="C124">
-        <v>0.3084874511606923</v>
+        <v>0.3043510328024827</v>
       </c>
       <c r="D124">
-        <v>0.9183043311200455</v>
+        <v>0.09658302374076433</v>
       </c>
       <c r="E124">
-        <v>0.358459560435424</v>
+        <v>0.9230575385509864</v>
       </c>
       <c r="F124">
-        <v>0.7251774238898477</v>
+        <v>0.5671554106670604</v>
       </c>
       <c r="G124">
-        <v>2.43004471022943</v>
+        <v>1.869950960099909</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,32 +8177,32 @@
         </is>
       </c>
       <c r="O124">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B125">
-        <v>1.406710971953635</v>
+        <v>1.402314935356395</v>
       </c>
       <c r="C125">
-        <v>0.3612321185495729</v>
+        <v>0.5450429606082595</v>
       </c>
       <c r="D125">
-        <v>0.9446954409910097</v>
+        <v>0.6203628351252941</v>
       </c>
       <c r="E125">
-        <v>0.3448143852263323</v>
+        <v>0.535018934802735</v>
       </c>
       <c r="F125">
-        <v>0.6929845274988551</v>
+        <v>0.4818414425036358</v>
       </c>
       <c r="G125">
-        <v>2.855526610033887</v>
+        <v>4.081191455234308</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8240,32 +8240,32 @@
         </is>
       </c>
       <c r="O125">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B126">
-        <v>0.9210459432313756</v>
+        <v>0.9481824462304904</v>
       </c>
       <c r="C126">
-        <v>0.197770560696257</v>
+        <v>0.2647184675564362</v>
       </c>
       <c r="D126">
-        <v>-0.4158625005071396</v>
+        <v>-0.2009997334356844</v>
       </c>
       <c r="E126">
-        <v>0.6775106210451409</v>
+        <v>0.8406987825017627</v>
       </c>
       <c r="F126">
-        <v>0.6250844389415183</v>
+        <v>0.5643689899706205</v>
       </c>
       <c r="G126">
-        <v>1.357137654841447</v>
+        <v>1.593017985248337</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8303,32 +8303,32 @@
         </is>
       </c>
       <c r="O126">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B127">
-        <v>1.257042158484617</v>
+        <v>1.119640703565869</v>
       </c>
       <c r="C127">
-        <v>0.3614379301084049</v>
+        <v>0.556212430703185</v>
       </c>
       <c r="D127">
-        <v>0.6329204794486971</v>
+        <v>0.2031738724520515</v>
       </c>
       <c r="E127">
-        <v>0.526785573408594</v>
+        <v>0.8389991336837049</v>
       </c>
       <c r="F127">
-        <v>0.6190038060282291</v>
+        <v>0.3763828263103758</v>
       </c>
       <c r="G127">
-        <v>2.552738727644598</v>
+        <v>3.330638959726936</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8366,32 +8366,32 @@
         </is>
       </c>
       <c r="O127">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B128">
-        <v>1.46383574588881</v>
+        <v>1.395411088780992</v>
       </c>
       <c r="C128">
-        <v>0.3087583109934213</v>
+        <v>0.4553069808358044</v>
       </c>
       <c r="D128">
-        <v>1.234169900034593</v>
+        <v>0.7317899201723727</v>
       </c>
       <c r="E128">
-        <v>0.2171396010324422</v>
+        <v>0.4642968023379379</v>
       </c>
       <c r="F128">
-        <v>0.7992392384759253</v>
+        <v>0.5716683718720545</v>
       </c>
       <c r="G128">
-        <v>2.681068430809273</v>
+        <v>3.406121805053701</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8429,32 +8429,32 @@
         </is>
       </c>
       <c r="O128">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B129">
-        <v>0.8858663589824378</v>
+        <v>0.9254496440896567</v>
       </c>
       <c r="C129">
-        <v>0.1849975391269756</v>
+        <v>0.2456153318510145</v>
       </c>
       <c r="D129">
-        <v>-0.6550853416150659</v>
+        <v>-0.3154345344667889</v>
       </c>
       <c r="E129">
-        <v>0.5124128091847928</v>
+        <v>0.7524317494556281</v>
       </c>
       <c r="F129">
-        <v>0.6164502297097927</v>
+        <v>0.5718533152618002</v>
       </c>
       <c r="G129">
-        <v>1.273029302537926</v>
+        <v>1.497686593551666</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8492,32 +8492,32 @@
         </is>
       </c>
       <c r="O129">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B130">
-        <v>1.330156791518551</v>
+        <v>1.134066771112026</v>
       </c>
       <c r="C130">
-        <v>0.3120245543251581</v>
+        <v>0.4738294428205274</v>
       </c>
       <c r="D130">
-        <v>0.914340937886199</v>
+        <v>0.2655176594227837</v>
       </c>
       <c r="E130">
-        <v>0.3605377258509388</v>
+        <v>0.7906107076676494</v>
       </c>
       <c r="F130">
-        <v>0.7216174954830612</v>
+        <v>0.4480374043858958</v>
       </c>
       <c r="G130">
-        <v>2.45187665362592</v>
+        <v>2.870535872118229</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.9512758029934745</v>
+        <v>0.9067163448166111</v>
       </c>
       <c r="C131">
-        <v>0.203663027552606</v>
+        <v>0.1900701630171613</v>
       </c>
       <c r="D131">
-        <v>-0.245264176909666</v>
+        <v>-0.5152077329214921</v>
       </c>
       <c r="E131">
-        <v>0.806251887429712</v>
+        <v>0.6064078659135634</v>
       </c>
       <c r="F131">
-        <v>0.6381873135607372</v>
+        <v>0.6247171499053779</v>
       </c>
       <c r="G131">
-        <v>1.417962460444235</v>
+        <v>1.31601082198899</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.9760521712233994</v>
+        <v>0.9428700958807769</v>
       </c>
       <c r="C132">
-        <v>0.1748985824519809</v>
+        <v>0.1564476477583432</v>
       </c>
       <c r="D132">
-        <v>-0.1385902591976972</v>
+        <v>-0.3760156378496465</v>
       </c>
       <c r="E132">
-        <v>0.8897739410584879</v>
+        <v>0.706905270391299</v>
       </c>
       <c r="F132">
-        <v>0.6927859773888271</v>
+        <v>0.6938784227810765</v>
       </c>
       <c r="G132">
-        <v>1.37514019054</v>
+        <v>1.28121006291431</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.815991308459532</v>
+        <v>0.7332047935778313</v>
       </c>
       <c r="C133">
-        <v>0.2156026637591948</v>
+        <v>0.2034857159351912</v>
       </c>
       <c r="D133">
-        <v>-0.9431774725172731</v>
+        <v>-1.525071299112945</v>
       </c>
       <c r="E133">
-        <v>0.3455901340672221</v>
+        <v>0.1272413149653022</v>
       </c>
       <c r="F133">
-        <v>0.5347665238208336</v>
+        <v>0.4920598617076535</v>
       </c>
       <c r="G133">
-        <v>1.245107511076331</v>
+        <v>1.092528188460344</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,32 +8744,32 @@
         </is>
       </c>
       <c r="O133">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B134">
-        <v>1.118513720897089</v>
+        <v>1.009022621838719</v>
       </c>
       <c r="C134">
-        <v>0.300313029302783</v>
+        <v>0.4228388530592445</v>
       </c>
       <c r="D134">
-        <v>0.3729467528036614</v>
+        <v>0.02124251618165114</v>
       </c>
       <c r="E134">
-        <v>0.7091880744681356</v>
+        <v>0.9830521989159603</v>
       </c>
       <c r="F134">
-        <v>0.6208896237256236</v>
+        <v>0.4405343918487732</v>
       </c>
       <c r="G134">
-        <v>2.014968355128947</v>
+        <v>2.311117293497907</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8807,32 +8807,32 @@
         </is>
       </c>
       <c r="O134">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B135">
-        <v>0.9501661058620151</v>
+        <v>0.8978287049699367</v>
       </c>
       <c r="C135">
-        <v>0.1904593669029109</v>
+        <v>0.2458086304120307</v>
       </c>
       <c r="D135">
-        <v>-0.2683956280395579</v>
+        <v>-0.4384548272310756</v>
       </c>
       <c r="E135">
-        <v>0.7883948044227096</v>
+        <v>0.6610566093119039</v>
       </c>
       <c r="F135">
-        <v>0.6541543402874315</v>
+        <v>0.5545756549944605</v>
       </c>
       <c r="G135">
-        <v>1.380126329716462</v>
+        <v>1.453537269817669</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8870,32 +8870,32 @@
         </is>
       </c>
       <c r="O135">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B136">
-        <v>0.954820103460599</v>
+        <v>0.7522214222664885</v>
       </c>
       <c r="C136">
-        <v>0.308552155321601</v>
+        <v>0.4404769335007028</v>
       </c>
       <c r="D136">
-        <v>-0.1498363527468873</v>
+        <v>-0.6464005994738637</v>
       </c>
       <c r="E136">
-        <v>0.8808937277614258</v>
+        <v>0.518019952280661</v>
       </c>
       <c r="F136">
-        <v>0.5215326277154514</v>
+        <v>0.3172568821269798</v>
       </c>
       <c r="G136">
-        <v>1.748081292566652</v>
+        <v>1.78352968838087</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8933,32 +8933,32 @@
         </is>
       </c>
       <c r="O136">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B137">
-        <v>0.9640383239469065</v>
+        <v>0.9173420852246739</v>
       </c>
       <c r="C137">
-        <v>0.2289363813114494</v>
+        <v>0.2319481632866935</v>
       </c>
       <c r="D137">
-        <v>-0.1599755784570377</v>
+        <v>-0.3719573668564159</v>
       </c>
       <c r="E137">
-        <v>0.8729003120009448</v>
+        <v>0.7099245918521497</v>
       </c>
       <c r="F137">
-        <v>0.6154932548993133</v>
+        <v>0.5822328214517491</v>
       </c>
       <c r="G137">
-        <v>1.509959504252233</v>
+        <v>1.445326457594921</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8996,32 +8996,32 @@
         </is>
       </c>
       <c r="O137">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B138">
-        <v>0.9675744645950854</v>
+        <v>0.9162937666752783</v>
       </c>
       <c r="C138">
-        <v>0.17471123464314</v>
+        <v>0.1672594999035715</v>
       </c>
       <c r="D138">
-        <v>-0.1886707006421573</v>
+        <v>-0.5226504909807612</v>
       </c>
       <c r="E138">
-        <v>0.8503509166301921</v>
+        <v>0.6012174972078542</v>
       </c>
       <c r="F138">
-        <v>0.6870208632114683</v>
+        <v>0.6601812531834392</v>
       </c>
       <c r="G138">
-        <v>1.362695654044933</v>
+        <v>1.271763266223311</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9059,32 +9059,32 @@
         </is>
       </c>
       <c r="O138">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B139">
-        <v>0.8258353735295784</v>
+        <v>0.7311970769142146</v>
       </c>
       <c r="C139">
-        <v>0.2389930492977811</v>
+        <v>0.2523562074005284</v>
       </c>
       <c r="D139">
-        <v>-0.8006920349428355</v>
+        <v>-1.240596614328205</v>
       </c>
       <c r="E139">
-        <v>0.4233099548134864</v>
+        <v>0.2147548033057875</v>
       </c>
       <c r="F139">
-        <v>0.516966294929692</v>
+        <v>0.4458907401188295</v>
       </c>
       <c r="G139">
-        <v>1.319242803373654</v>
+        <v>1.19905868676575</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>1.499766553366728</v>
+        <v>1.286043715869936</v>
       </c>
       <c r="C140">
-        <v>0.4630434414730312</v>
+        <v>0.5301106239120958</v>
       </c>
       <c r="D140">
-        <v>0.8753162848353352</v>
+        <v>0.47456249237026</v>
       </c>
       <c r="E140">
-        <v>0.3814018357783699</v>
+        <v>0.6350988456951697</v>
       </c>
       <c r="F140">
-        <v>0.6051741545241404</v>
+        <v>0.4550139906720735</v>
       </c>
       <c r="G140">
-        <v>3.716780860157816</v>
+        <v>3.634851835403272</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.179529876477695</v>
+        <v>1.344982473506826</v>
       </c>
       <c r="C141">
-        <v>0.3914156994361297</v>
+        <v>0.3969780137270699</v>
       </c>
       <c r="D141">
-        <v>0.4218429397811995</v>
+        <v>0.7465929393327168</v>
       </c>
       <c r="E141">
-        <v>0.6731396611507977</v>
+        <v>0.4553093117283672</v>
       </c>
       <c r="F141">
-        <v>0.5476906139487617</v>
+        <v>0.6177437031043824</v>
       </c>
       <c r="G141">
-        <v>2.540285873209515</v>
+        <v>2.928363081565674</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>2.06266413732298</v>
+        <v>1.398916129323247</v>
       </c>
       <c r="C142">
-        <v>0.4815480475448909</v>
+        <v>0.5523337931646314</v>
       </c>
       <c r="D142">
-        <v>1.503481161399792</v>
+        <v>0.6077805623929726</v>
       </c>
       <c r="E142">
-        <v>0.1327150112855703</v>
+        <v>0.5433330226756821</v>
       </c>
       <c r="F142">
-        <v>0.8026645388006054</v>
+        <v>0.4738537265876525</v>
       </c>
       <c r="G142">
-        <v>5.300574695570623</v>
+        <v>4.129895423580129</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,32 +9311,32 @@
         </is>
       </c>
       <c r="O142">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B143">
-        <v>1.148656961155554</v>
+        <v>1.388294750273747</v>
       </c>
       <c r="C143">
-        <v>0.5164017143370012</v>
+        <v>0.8729510590745108</v>
       </c>
       <c r="D143">
-        <v>0.2683829200850278</v>
+        <v>0.3758242712862656</v>
       </c>
       <c r="E143">
-        <v>0.7884045852139479</v>
+        <v>0.7070475425037452</v>
       </c>
       <c r="F143">
-        <v>0.4174730191271782</v>
+        <v>0.2508559421161227</v>
       </c>
       <c r="G143">
-        <v>3.160474459330671</v>
+        <v>7.683143948591254</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9374,32 +9374,32 @@
         </is>
       </c>
       <c r="O143">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B144">
-        <v>1.468408107957415</v>
+        <v>1.749691813620089</v>
       </c>
       <c r="C144">
-        <v>0.4317387430354748</v>
+        <v>0.6318371312639565</v>
       </c>
       <c r="D144">
-        <v>0.8898411376088953</v>
+        <v>0.8854175201842228</v>
       </c>
       <c r="E144">
-        <v>0.3735511940285988</v>
+        <v>0.375931486446703</v>
       </c>
       <c r="F144">
-        <v>0.6300138392164436</v>
+        <v>0.5071551251375939</v>
       </c>
       <c r="G144">
-        <v>3.422500010788328</v>
+        <v>6.036459637115129</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9437,32 +9437,32 @@
         </is>
       </c>
       <c r="O144">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B145">
-        <v>1.499499993353935</v>
+        <v>1.611763585794822</v>
       </c>
       <c r="C145">
-        <v>0.5121576328523005</v>
+        <v>0.886541811549337</v>
       </c>
       <c r="D145">
-        <v>0.7910293409442822</v>
+        <v>0.5384167652042934</v>
       </c>
       <c r="E145">
-        <v>0.42892686989331</v>
+        <v>0.5902893545633969</v>
       </c>
       <c r="F145">
-        <v>0.5495372052203917</v>
+        <v>0.2835799891218367</v>
       </c>
       <c r="G145">
-        <v>4.091625114202576</v>
+        <v>9.160667029217199</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9500,32 +9500,32 @@
         </is>
       </c>
       <c r="O145">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B146">
-        <v>1.347269189815046</v>
+        <v>1.466421674113632</v>
       </c>
       <c r="C146">
-        <v>0.4450897105523263</v>
+        <v>0.7517739648342484</v>
       </c>
       <c r="D146">
-        <v>0.6697070598483906</v>
+        <v>0.5092291244890935</v>
       </c>
       <c r="E146">
-        <v>0.5030445503263836</v>
+        <v>0.6105916307791115</v>
       </c>
       <c r="F146">
-        <v>0.5631101165047023</v>
+        <v>0.3360065256387034</v>
       </c>
       <c r="G146">
-        <v>3.223409092863867</v>
+        <v>6.399853461841607</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9563,32 +9563,32 @@
         </is>
       </c>
       <c r="O146">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B147">
-        <v>1.237941063702309</v>
+        <v>1.561618504677224</v>
       </c>
       <c r="C147">
-        <v>0.3885799149910812</v>
+        <v>0.5782766778558204</v>
       </c>
       <c r="D147">
-        <v>0.5493067419035441</v>
+        <v>0.770777732344468</v>
       </c>
       <c r="E147">
-        <v>0.5827949614099902</v>
+        <v>0.4408386881743289</v>
       </c>
       <c r="F147">
-        <v>0.5780163801073437</v>
+        <v>0.5027417424281738</v>
       </c>
       <c r="G147">
-        <v>2.651305620293674</v>
+        <v>4.850705935759327</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9626,32 +9626,32 @@
         </is>
       </c>
       <c r="O147">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B148">
-        <v>1.805515252277153</v>
+        <v>1.69320520350805</v>
       </c>
       <c r="C148">
-        <v>0.4521412290278083</v>
+        <v>0.7864147209642071</v>
       </c>
       <c r="D148">
-        <v>1.306773130698776</v>
+        <v>0.6696508709730593</v>
       </c>
       <c r="E148">
-        <v>0.1912897731911893</v>
+        <v>0.5030803769924523</v>
       </c>
       <c r="F148">
-        <v>0.7442825718023403</v>
+        <v>0.3625034718694974</v>
       </c>
       <c r="G148">
-        <v>4.379902808030769</v>
+        <v>7.908734905079327</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.8148376634492306</v>
+        <v>0.8024591162280647</v>
       </c>
       <c r="C149">
-        <v>0.2822910168895661</v>
+        <v>0.270316881209457</v>
       </c>
       <c r="D149">
-        <v>-0.7253733178955559</v>
+        <v>-0.814134765839527</v>
       </c>
       <c r="E149">
-        <v>0.4682230374969227</v>
+        <v>0.4155677513439782</v>
       </c>
       <c r="F149">
-        <v>0.4685808604765535</v>
+        <v>0.4724205367558377</v>
       </c>
       <c r="G149">
-        <v>1.416960174387286</v>
+        <v>1.36306655430252</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>1.160201965292188</v>
+        <v>1.221411272309219</v>
       </c>
       <c r="C150">
-        <v>0.3239809611572133</v>
+        <v>0.2982119567605815</v>
       </c>
       <c r="D150">
-        <v>0.4586507103472468</v>
+        <v>0.6706872955196161</v>
       </c>
       <c r="E150">
-        <v>0.6464850147403385</v>
+        <v>0.5024197578727443</v>
       </c>
       <c r="F150">
-        <v>0.61483771898124</v>
+        <v>0.6808061118988036</v>
       </c>
       <c r="G150">
-        <v>2.189307127250153</v>
+        <v>2.191292748478992</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.8115424111797869</v>
+        <v>0.637375755798792</v>
       </c>
       <c r="C151">
-        <v>0.3009919607087118</v>
+        <v>0.3014667325144587</v>
       </c>
       <c r="D151">
-        <v>-0.6937681332186192</v>
+        <v>-1.494015309920396</v>
       </c>
       <c r="E151">
-        <v>0.4878276300807134</v>
+        <v>0.1351716177328914</v>
       </c>
       <c r="F151">
-        <v>0.4498900617356034</v>
+        <v>0.3530096617334845</v>
       </c>
       <c r="G151">
-        <v>1.463915612189176</v>
+        <v>1.150812281128981</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,32 +9878,32 @@
         </is>
       </c>
       <c r="O151">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B152">
-        <v>0.9137975571920856</v>
+        <v>0.8414564441645382</v>
       </c>
       <c r="C152">
-        <v>0.4053348763067682</v>
+        <v>0.5826887110330968</v>
       </c>
       <c r="D152">
-        <v>-0.2223993748557423</v>
+        <v>-0.2962491347082061</v>
       </c>
       <c r="E152">
-        <v>0.8240029984291182</v>
+        <v>0.7670398278735816</v>
       </c>
       <c r="F152">
-        <v>0.4128842538438547</v>
+        <v>0.2685629574096456</v>
       </c>
       <c r="G152">
-        <v>2.022421460146103</v>
+        <v>2.636435621112202</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9941,32 +9941,32 @@
         </is>
       </c>
       <c r="O152">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B153">
-        <v>1.286700794937199</v>
+        <v>1.242408477974664</v>
       </c>
       <c r="C153">
-        <v>0.3916193122003083</v>
+        <v>0.5152753719527148</v>
       </c>
       <c r="D153">
-        <v>0.6436899590143631</v>
+        <v>0.4212346029179713</v>
       </c>
       <c r="E153">
-        <v>0.5197765023567611</v>
+        <v>0.6735837789970486</v>
       </c>
       <c r="F153">
-        <v>0.597214861371704</v>
+        <v>0.45254442021014</v>
       </c>
       <c r="G153">
-        <v>2.772199827528373</v>
+        <v>3.410889091122939</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10004,32 +10004,32 @@
         </is>
       </c>
       <c r="O153">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B154">
-        <v>0.9116575790453557</v>
+        <v>0.6754689688828175</v>
       </c>
       <c r="C154">
-        <v>0.4127670266736198</v>
+        <v>0.6122779627000374</v>
       </c>
       <c r="D154">
-        <v>-0.22407511987957</v>
+        <v>-0.6408005587922674</v>
       </c>
       <c r="E154">
-        <v>0.8226988517272529</v>
+        <v>0.5216522698430035</v>
       </c>
       <c r="F154">
-        <v>0.4059605355149024</v>
+        <v>0.2034386454632037</v>
       </c>
       <c r="G154">
-        <v>2.047291469789505</v>
+        <v>2.242731841262386</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10067,32 +10067,32 @@
         </is>
       </c>
       <c r="O154">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B155">
-        <v>0.8008339886777502</v>
+        <v>0.7857931618344638</v>
       </c>
       <c r="C155">
-        <v>0.3087058600634314</v>
+        <v>0.3211828904546778</v>
       </c>
       <c r="D155">
-        <v>-0.7194602928250262</v>
+        <v>-0.750543323540155</v>
       </c>
       <c r="E155">
-        <v>0.4718573591828386</v>
+        <v>0.4529275413212864</v>
       </c>
       <c r="F155">
-        <v>0.4372920606913534</v>
+        <v>0.4187134129131507</v>
       </c>
       <c r="G155">
-        <v>1.466605811245629</v>
+        <v>1.474686203362392</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10130,32 +10130,32 @@
         </is>
       </c>
       <c r="O155">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B156">
-        <v>1.159825391288472</v>
+        <v>1.140540376275274</v>
       </c>
       <c r="C156">
-        <v>0.3265630949478862</v>
+        <v>0.322732152743108</v>
       </c>
       <c r="D156">
-        <v>0.4540300827949646</v>
+        <v>0.4074653338874396</v>
       </c>
       <c r="E156">
-        <v>0.6498071748072973</v>
+        <v>0.6836662501121937</v>
       </c>
       <c r="F156">
-        <v>0.6115353996063631</v>
+        <v>0.6058994494645477</v>
       </c>
       <c r="G156">
-        <v>2.19970084993173</v>
+        <v>2.146944267838056</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10193,32 +10193,32 @@
         </is>
       </c>
       <c r="O156">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B157">
-        <v>0.795502159537975</v>
+        <v>0.6340480380435886</v>
       </c>
       <c r="C157">
-        <v>0.3208050147555171</v>
+        <v>0.3599697323189309</v>
       </c>
       <c r="D157">
-        <v>-0.7131488162356757</v>
+        <v>-1.265746857924072</v>
       </c>
       <c r="E157">
-        <v>0.4757536747832806</v>
+        <v>0.2056037264382345</v>
       </c>
       <c r="F157">
-        <v>0.4242009524808875</v>
+        <v>0.313123289917235</v>
       </c>
       <c r="G157">
-        <v>1.491801661756273</v>
+        <v>1.283893365623443</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
   </sheetData>
